--- a/www/flightdata/xlsx/eoss-340.xlsx
+++ b/www/flightdata/xlsx/eoss-340.xlsx
@@ -3579,7 +3579,7 @@
         <v>28050.44</v>
       </c>
       <c r="I2">
-        <v>628</v>
+        <v>460</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
